--- a/order_forms/037_graphic_design_subscription_form--order_forms.xlsx
+++ b/order_forms/037_graphic_design_subscription_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'phone', 'label': 'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'e-mail',_'label':_'e-mail'}</t>
+          <t>e-mail</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'e-mail', 'label': 'e-mail'}</t>
+          <t>e-mail</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'in_app',_'label':_'in_app'}</t>
+          <t>in_app</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'in app', 'label': 'in app'}</t>
+          <t>in app</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'basic',_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'basic', 'label': 'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'premium',_'label':_'premium'}</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'premium', 'label': 'premium'}</t>
+          <t>premium</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'enterprise',_'label':_'enterprise'}</t>
+          <t>enterprise</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'enterprise', 'label': 'enterprise'}</t>
+          <t>enterprise</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_31,_'name':_'web_design',_'label':_'web_design'}</t>
+          <t>web_design</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 31, 'name': 'web design', 'label': 'web design'}</t>
+          <t>web design</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_32,_'name':_'print_media',_'label':_'print_media'}</t>
+          <t>print_media</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 32, 'name': 'print media', 'label': 'print media'}</t>
+          <t>print media</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_33,_'name':_'branding',_'label':_'branding'}</t>
+          <t>branding</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 33, 'name': 'branding', 'label': 'branding'}</t>
+          <t>branding</t>
         </is>
       </c>
     </row>
